--- a/NEW BOT 02/Ground_Floor_Fan_Store_Stock_Detail.xlsx
+++ b/NEW BOT 02/Ground_Floor_Fan_Store_Stock_Detail.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Warehouse Module ⟶ Warehouse Reports ⟶ Stock Position Report Detail(Closing)(91223) ⟶ Warehouse: Ground Floor Fan Store (FAN-1)  |  Date Range: 2026-09-01 to 2026-09-19</t>
+          <t>Warehouse Module ⟶ Warehouse Reports ⟶ Stock Position Report Detail(Closing)(91223) ⟶ Warehouse: Ground Floor Fan Store (FAN-1)  |  Date Range: 2026-09-01 to 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -634,18 +634,18 @@
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2,183,861.83</t>
+          <t>2,208,700.83</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>4,397,540.46</t>
+          <t>4,357,413.44</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>16988.50002</v>
+        <v>1364.50002</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>16988.50002</v>
+        <v>1364.50002</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -888,10 +888,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>3357.628</v>
+        <v>7750.956</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>3357.628</v>
+        <v>7750.956</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -934,10 +934,10 @@
         <v>32000</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>482.654</v>
+        <v>365.154</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>32482.654</v>
+        <v>32365.154</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1026,10 +1026,10 @@
         <v>73542</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>14480.028</v>
+        <v>12278.787</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>88022.02800000001</v>
+        <v>85820.787</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>17818.881</v>
+        <v>8870.249</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>17818.881</v>
+        <v>8870.249</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>20056.04</v>
+        <v>17554.04</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>20056.04</v>
+        <v>17554.04</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1440,10 +1440,10 @@
         <v>73.16</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>2149.29</v>
+        <v>1555.29</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>2222.45</v>
+        <v>1628.45</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1578,10 +1578,10 @@
         <v>1563.45</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>129.508</v>
+        <v>123.208</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>1692.958</v>
+        <v>1686.658</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1624,10 +1624,10 @@
         <v>1818.74</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>179.465</v>
+        <v>163.265</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>1998.205</v>
+        <v>1982.005</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1670,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>54.525</v>
+        <v>52.725</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>54.525</v>
+        <v>52.725</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1716,10 +1716,10 @@
         <v>4780</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>5426.36</v>
+        <v>4828.05</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>10206.36</v>
+        <v>9608.049999999999</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -1762,10 +1762,10 @@
         <v>1100</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>6958.666</v>
+        <v>6950.826</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>8058.666</v>
+        <v>8050.826</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="H25" s="19" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>83.224</v>
+        <v>438.37</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>2083.224</v>
+        <v>1938.37</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="H27" s="19" t="n">
-        <v>935</v>
+        <v>835</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>166.083</v>
+        <v>233.683</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>1101.083</v>
+        <v>1068.683</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="H28" s="16" t="n">
-        <v>3940</v>
+        <v>3820</v>
       </c>
       <c r="I28" s="16" t="n">
-        <v>163.536</v>
+        <v>251.136</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>4103.536</v>
+        <v>4071.136</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="H30" s="16" t="n">
-        <v>43700</v>
+        <v>33700</v>
       </c>
       <c r="I30" s="16" t="n">
-        <v>3526</v>
+        <v>10426</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>47226</v>
+        <v>44126</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -2084,10 +2084,10 @@
         <v>4800</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>4616</v>
+        <v>4567</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>9416</v>
+        <v>9367</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -2222,10 +2222,10 @@
         <v>2800</v>
       </c>
       <c r="I34" s="16" t="n">
-        <v>2706</v>
+        <v>2657</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>5506</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -2314,10 +2314,10 @@
         <v>26</v>
       </c>
       <c r="I36" s="16" t="n">
-        <v>10.85928</v>
+        <v>8.91958</v>
       </c>
       <c r="J36" s="16" t="n">
-        <v>36.85928</v>
+        <v>34.91958</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -2406,10 +2406,10 @@
         <v>2</v>
       </c>
       <c r="I38" s="16" t="n">
-        <v>1.0743</v>
+        <v>1.0694</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>3.0743</v>
+        <v>3.0694</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2452,10 +2452,10 @@
         <v>1980</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>1120.33</v>
+        <v>890.598</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>3100.33</v>
+        <v>2870.598</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2498,10 +2498,10 @@
         <v>450</v>
       </c>
       <c r="I40" s="16" t="n">
-        <v>290.8115</v>
+        <v>271.0655</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>740.8115</v>
+        <v>721.0654999999999</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2544,10 +2544,10 @@
         <v>350</v>
       </c>
       <c r="I41" s="19" t="n">
-        <v>119.4587</v>
+        <v>107.6867</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>469.4587</v>
+        <v>457.6867</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2590,10 +2590,10 @@
         <v>420</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>102.52445</v>
+        <v>83.21044999999999</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>522.52445</v>
+        <v>503.21045</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2636,10 +2636,10 @@
         <v>525</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>162.971</v>
+        <v>141.097</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>687.971</v>
+        <v>666.097</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2682,10 +2682,10 @@
         <v>50</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>106.896</v>
+        <v>104.352</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>156.896</v>
+        <v>154.352</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="H45" s="19" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>95.24845000000001</v>
+        <v>142.70445</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>170.24845</v>
+        <v>167.70445</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2774,10 +2774,10 @@
         <v>120</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>54.677</v>
+        <v>40.757</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>174.677</v>
+        <v>160.757</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2912,10 +2912,10 @@
         <v>30</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>44.68655</v>
+        <v>43.58063</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>74.68655</v>
+        <v>73.58063</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>8.048</v>
+        <v>8.0235</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>8.048</v>
+        <v>8.0235</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -3004,10 +3004,10 @@
         <v>130000</v>
       </c>
       <c r="I51" s="19" t="n">
-        <v>7766</v>
+        <v>7717</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>137766</v>
+        <v>137717</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -3188,10 +3188,10 @@
         <v>66200</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>19653</v>
+        <v>18083</v>
       </c>
       <c r="J55" s="19" t="n">
-        <v>85853</v>
+        <v>84283</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -3234,10 +3234,10 @@
         <v>20000</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>11305</v>
+        <v>11256</v>
       </c>
       <c r="J56" s="16" t="n">
-        <v>31305</v>
+        <v>31256</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -3326,10 +3326,10 @@
         <v>2300</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>152.163</v>
+        <v>130.779</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>2452.163</v>
+        <v>2430.779</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -3372,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="19" t="n">
-        <v>29.2023</v>
+        <v>26.4151</v>
       </c>
       <c r="J59" s="19" t="n">
-        <v>29.2023</v>
+        <v>26.4151</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -3418,10 +3418,10 @@
         <v>325</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>228.45</v>
+        <v>203.6</v>
       </c>
       <c r="J60" s="16" t="n">
-        <v>553.45</v>
+        <v>528.6</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -3464,10 +3464,10 @@
         <v>30750</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>24468</v>
+        <v>22898</v>
       </c>
       <c r="J61" s="19" t="n">
-        <v>55218</v>
+        <v>53648</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -3510,10 +3510,10 @@
         <v>150</v>
       </c>
       <c r="I62" s="16" t="n">
-        <v>76.178</v>
+        <v>75.982</v>
       </c>
       <c r="J62" s="16" t="n">
-        <v>226.178</v>
+        <v>225.982</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="I63" s="19" t="n">
-        <v>123.9674</v>
+        <v>119.2654</v>
       </c>
       <c r="J63" s="19" t="n">
-        <v>123.9674</v>
+        <v>119.2654</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -3602,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="16" t="n">
-        <v>100.194</v>
+        <v>99.252</v>
       </c>
       <c r="J64" s="16" t="n">
-        <v>100.194</v>
+        <v>99.252</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -3648,10 +3648,10 @@
         <v>742</v>
       </c>
       <c r="I65" s="19" t="n">
-        <v>38421</v>
+        <v>34791</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>39163</v>
+        <v>35533</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -3694,10 +3694,10 @@
         <v>2506</v>
       </c>
       <c r="I66" s="16" t="n">
-        <v>9723</v>
+        <v>8383</v>
       </c>
       <c r="J66" s="16" t="n">
-        <v>12229</v>
+        <v>10889</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -3740,10 +3740,10 @@
         <v>25295</v>
       </c>
       <c r="I67" s="19" t="n">
-        <v>230884</v>
+        <v>225914</v>
       </c>
       <c r="J67" s="19" t="n">
-        <v>256179</v>
+        <v>251209</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="I68" s="16" t="n">
-        <v>339.482</v>
+        <v>336.244</v>
       </c>
       <c r="J68" s="16" t="n">
-        <v>339.482</v>
+        <v>336.244</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -3832,10 +3832,10 @@
         <v>6.4</v>
       </c>
       <c r="I69" s="19" t="n">
-        <v>246.404</v>
+        <v>245.62</v>
       </c>
       <c r="J69" s="19" t="n">
-        <v>252.804</v>
+        <v>252.02</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -3924,10 +3924,10 @@
         <v>457.95</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>832.9915</v>
+        <v>831.8155</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>1290.9415</v>
+        <v>1289.7655</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="H72" s="16" t="n">
-        <v>0</v>
+        <v>7888</v>
       </c>
       <c r="I72" s="16" t="n">
-        <v>1838</v>
+        <v>38</v>
       </c>
       <c r="J72" s="16" t="n">
-        <v>1838</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -4062,10 +4062,10 @@
         <v>21989</v>
       </c>
       <c r="I74" s="16" t="n">
-        <v>21773</v>
+        <v>21724</v>
       </c>
       <c r="J74" s="16" t="n">
-        <v>43762</v>
+        <v>43713</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -4108,10 +4108,10 @@
         <v>55207</v>
       </c>
       <c r="I75" s="19" t="n">
-        <v>78254</v>
+        <v>78107</v>
       </c>
       <c r="J75" s="19" t="n">
-        <v>133461</v>
+        <v>133314</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -4200,10 +4200,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="19" t="n">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="J77" s="19" t="n">
-        <v>615</v>
+        <v>566</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -4243,13 +4243,13 @@
         </is>
       </c>
       <c r="H78" s="16" t="n">
-        <v>12702</v>
+        <v>28082</v>
       </c>
       <c r="I78" s="16" t="n">
-        <v>70242</v>
+        <v>68542</v>
       </c>
       <c r="J78" s="16" t="n">
-        <v>82944</v>
+        <v>96624</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="I79" s="19" t="n">
-        <v>136811</v>
+        <v>135011</v>
       </c>
       <c r="J79" s="19" t="n">
-        <v>136811</v>
+        <v>135011</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -4384,10 +4384,10 @@
         <v>19570</v>
       </c>
       <c r="I81" s="19" t="n">
-        <v>19058.42</v>
+        <v>18068.085</v>
       </c>
       <c r="J81" s="19" t="n">
-        <v>38628.42</v>
+        <v>37638.085</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -4430,10 +4430,10 @@
         <v>1900</v>
       </c>
       <c r="I82" s="16" t="n">
-        <v>3017.4032</v>
+        <v>2545.0532</v>
       </c>
       <c r="J82" s="16" t="n">
-        <v>4917.403200000001</v>
+        <v>4445.0532</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -4522,10 +4522,10 @@
         <v>12</v>
       </c>
       <c r="I84" s="16" t="n">
-        <v>11.698</v>
+        <v>11.6735</v>
       </c>
       <c r="J84" s="16" t="n">
-        <v>23.698</v>
+        <v>23.6735</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -4614,10 +4614,10 @@
         <v>26.46</v>
       </c>
       <c r="I86" s="16" t="n">
-        <v>49.3779</v>
+        <v>38.6054</v>
       </c>
       <c r="J86" s="16" t="n">
-        <v>75.83789999999999</v>
+        <v>65.06540000000001</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -4752,10 +4752,10 @@
         <v>18100</v>
       </c>
       <c r="I89" s="19" t="n">
-        <v>11034.32</v>
+        <v>10073.875</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>29134.32</v>
+        <v>28173.875</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -4798,10 +4798,10 @@
         <v>4500</v>
       </c>
       <c r="I90" s="16" t="n">
-        <v>15189.0815</v>
+        <v>14198.7465</v>
       </c>
       <c r="J90" s="16" t="n">
-        <v>19689.0815</v>
+        <v>18698.7465</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -5672,10 +5672,10 @@
         <v>111600</v>
       </c>
       <c r="I109" s="19" t="n">
-        <v>8487</v>
+        <v>8438</v>
       </c>
       <c r="J109" s="19" t="n">
-        <v>120087</v>
+        <v>120038</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -5718,10 +5718,10 @@
         <v>112500</v>
       </c>
       <c r="I110" s="16" t="n">
-        <v>8368</v>
+        <v>8319</v>
       </c>
       <c r="J110" s="16" t="n">
-        <v>120868</v>
+        <v>120819</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -5764,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="I111" s="19" t="n">
-        <v>66906</v>
+        <v>63757</v>
       </c>
       <c r="J111" s="19" t="n">
-        <v>66906</v>
+        <v>63757</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -5810,10 +5810,10 @@
         <v>176658</v>
       </c>
       <c r="I112" s="16" t="n">
-        <v>152202</v>
+        <v>143130</v>
       </c>
       <c r="J112" s="16" t="n">
-        <v>328860</v>
+        <v>319788</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="H120" s="16" t="n">
-        <v>85</v>
+        <v>1864</v>
       </c>
       <c r="I120" s="16" t="n">
         <v>1369</v>
       </c>
       <c r="J120" s="16" t="n">
-        <v>1454</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="H122" s="16" t="n">
-        <v>1925</v>
+        <v>12425</v>
       </c>
       <c r="I122" s="16" t="n">
         <v>3765</v>
       </c>
       <c r="J122" s="16" t="n">
-        <v>5690</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -10913,13 +10913,13 @@
         </is>
       </c>
       <c r="H223" s="19" t="n">
-        <v>229105</v>
+        <v>248885</v>
       </c>
       <c r="I223" s="19" t="n">
-        <v>30558</v>
+        <v>19941</v>
       </c>
       <c r="J223" s="19" t="n">
-        <v>259663</v>
+        <v>268826</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
@@ -10962,10 +10962,10 @@
         <v>22080</v>
       </c>
       <c r="I224" s="16" t="n">
-        <v>29491.5</v>
+        <v>25927.02</v>
       </c>
       <c r="J224" s="16" t="n">
-        <v>51571.5</v>
+        <v>48007.02</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
@@ -11146,10 +11146,10 @@
         <v>7500</v>
       </c>
       <c r="I228" s="16" t="n">
-        <v>1093</v>
+        <v>1044</v>
       </c>
       <c r="J228" s="16" t="n">
-        <v>8593</v>
+        <v>8544</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
@@ -11284,10 +11284,10 @@
         <v>88500</v>
       </c>
       <c r="I231" s="19" t="n">
-        <v>48582</v>
+        <v>46782</v>
       </c>
       <c r="J231" s="19" t="n">
-        <v>137082</v>
+        <v>135282</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
@@ -11376,10 +11376,10 @@
         <v>0</v>
       </c>
       <c r="I233" s="19" t="n">
-        <v>41730</v>
+        <v>40160</v>
       </c>
       <c r="J233" s="19" t="n">
-        <v>41730</v>
+        <v>40160</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
@@ -11419,13 +11419,13 @@
         </is>
       </c>
       <c r="H234" s="16" t="n">
-        <v>98500</v>
+        <v>78500</v>
       </c>
       <c r="I234" s="16" t="n">
-        <v>27233</v>
+        <v>47184</v>
       </c>
       <c r="J234" s="16" t="n">
-        <v>125733</v>
+        <v>125684</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
@@ -11514,10 +11514,10 @@
         <v>5000</v>
       </c>
       <c r="I236" s="16" t="n">
-        <v>1616</v>
+        <v>1567</v>
       </c>
       <c r="J236" s="16" t="n">
-        <v>6616</v>
+        <v>6567</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1">
@@ -11649,13 +11649,13 @@
         </is>
       </c>
       <c r="H239" s="19" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="I239" s="19" t="n">
-        <v>4813</v>
+        <v>4764</v>
       </c>
       <c r="J239" s="19" t="n">
-        <v>4813</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
@@ -11787,13 +11787,13 @@
         </is>
       </c>
       <c r="H242" s="16" t="n">
-        <v>8650</v>
+        <v>7650</v>
       </c>
       <c r="I242" s="16" t="n">
-        <v>6734</v>
+        <v>8734</v>
       </c>
       <c r="J242" s="16" t="n">
-        <v>15384</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
@@ -11974,10 +11974,10 @@
         <v>518</v>
       </c>
       <c r="I246" s="16" t="n">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="J246" s="16" t="n">
-        <v>910</v>
+        <v>861</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -12109,13 +12109,13 @@
         </is>
       </c>
       <c r="H249" s="19" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
       <c r="I249" s="19" t="n">
-        <v>5680</v>
+        <v>4310</v>
       </c>
       <c r="J249" s="19" t="n">
-        <v>12580</v>
+        <v>12210</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1">
@@ -12250,10 +12250,10 @@
         <v>0</v>
       </c>
       <c r="I252" s="16" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="J252" s="16" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1">
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="H253" s="19" t="n">
-        <v>2115</v>
+        <v>315</v>
       </c>
       <c r="I253" s="19" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="J253" s="19" t="n">
-        <v>2245</v>
+        <v>585</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="H254" s="16" t="n">
-        <v>1250</v>
+        <v>1210</v>
       </c>
       <c r="I254" s="16" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="J254" s="16" t="n">
         <v>1303</v>
@@ -12388,10 +12388,10 @@
         <v>650</v>
       </c>
       <c r="I255" s="19" t="n">
-        <v>248.218</v>
+        <v>247.728</v>
       </c>
       <c r="J255" s="19" t="n">
-        <v>898.218</v>
+        <v>897.7280000000001</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
@@ -12480,10 +12480,10 @@
         <v>431.5</v>
       </c>
       <c r="I257" s="19" t="n">
-        <v>150.767</v>
+        <v>120.576</v>
       </c>
       <c r="J257" s="19" t="n">
-        <v>582.2670000000001</v>
+        <v>552.076</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
@@ -12572,10 +12572,10 @@
         <v>124.4</v>
       </c>
       <c r="I259" s="19" t="n">
-        <v>149.42</v>
+        <v>146.72</v>
       </c>
       <c r="J259" s="19" t="n">
-        <v>273.82</v>
+        <v>271.12</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1">
@@ -12618,10 +12618,10 @@
         <v>140</v>
       </c>
       <c r="I260" s="16" t="n">
-        <v>217.092</v>
+        <v>208.362</v>
       </c>
       <c r="J260" s="16" t="n">
-        <v>357.092</v>
+        <v>348.362</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -12664,10 +12664,10 @@
         <v>87.45999999999999</v>
       </c>
       <c r="I261" s="19" t="n">
-        <v>42.2191</v>
+        <v>41.7763</v>
       </c>
       <c r="J261" s="19" t="n">
-        <v>129.6791</v>
+        <v>129.2363</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -12710,10 +12710,10 @@
         <v>44952</v>
       </c>
       <c r="I262" s="16" t="n">
-        <v>42595.779</v>
+        <v>40508.1198</v>
       </c>
       <c r="J262" s="16" t="n">
-        <v>87547.77900000001</v>
+        <v>85460.1198</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -13216,10 +13216,10 @@
         <v>65300</v>
       </c>
       <c r="I273" s="19" t="n">
-        <v>29860</v>
+        <v>29811</v>
       </c>
       <c r="J273" s="19" t="n">
-        <v>95160</v>
+        <v>95111</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1">
@@ -13676,10 +13676,10 @@
         <v>0</v>
       </c>
       <c r="I283" s="19" t="n">
-        <v>71.62560000000001</v>
+        <v>182.0208</v>
       </c>
       <c r="J283" s="19" t="n">
-        <v>71.62560000000001</v>
+        <v>182.0208</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -13722,10 +13722,10 @@
         <v>0</v>
       </c>
       <c r="I284" s="16" t="n">
-        <v>954.136</v>
+        <v>3697.5312</v>
       </c>
       <c r="J284" s="16" t="n">
-        <v>954.136</v>
+        <v>3697.5312</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1">
@@ -13768,10 +13768,10 @@
         <v>0</v>
       </c>
       <c r="I285" s="19" t="n">
-        <v>1744.4896</v>
+        <v>3744.4896</v>
       </c>
       <c r="J285" s="19" t="n">
-        <v>1744.4896</v>
+        <v>3744.4896</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1">
@@ -13814,10 +13814,10 @@
         <v>0</v>
       </c>
       <c r="I286" s="16" t="n">
-        <v>9100</v>
+        <v>28</v>
       </c>
       <c r="J286" s="16" t="n">
-        <v>9100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -13906,10 +13906,10 @@
         <v>0</v>
       </c>
       <c r="I288" s="16" t="n">
-        <v>26.77024</v>
+        <v>18.96832</v>
       </c>
       <c r="J288" s="16" t="n">
-        <v>26.77024</v>
+        <v>18.96832</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1">
@@ -14228,10 +14228,10 @@
         <v>102.07</v>
       </c>
       <c r="I295" s="19" t="n">
-        <v>32.5335</v>
+        <v>29.2114</v>
       </c>
       <c r="J295" s="19" t="n">
-        <v>134.6035</v>
+        <v>131.2814</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1">
@@ -14869,13 +14869,13 @@
         </is>
       </c>
       <c r="H309" s="19" t="n">
-        <v>2166</v>
+        <v>2070</v>
       </c>
       <c r="I309" s="19" t="n">
         <v>3720</v>
       </c>
       <c r="J309" s="19" t="n">
-        <v>5886</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1">
@@ -15421,13 +15421,13 @@
         </is>
       </c>
       <c r="H321" s="19" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="I321" s="19" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="J321" s="19" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1">
@@ -15651,13 +15651,13 @@
         </is>
       </c>
       <c r="H326" s="16" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I326" s="16" t="n">
         <v>153</v>
       </c>
       <c r="J326" s="16" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1">
@@ -16111,13 +16111,13 @@
         </is>
       </c>
       <c r="H336" s="16" t="n">
-        <v>57000</v>
+        <v>56000</v>
       </c>
       <c r="I336" s="16" t="n">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="J336" s="16" t="n">
-        <v>70000</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1">
@@ -16689,13 +16689,13 @@
       </c>
       <c r="G349" s="20" t="n"/>
       <c r="H349" s="21" t="n">
-        <v>2183861.832</v>
+        <v>2208700.832</v>
       </c>
       <c r="I349" s="21" t="n">
-        <v>2213678.62913</v>
+        <v>2148712.61129</v>
       </c>
       <c r="J349" s="21" t="n">
-        <v>4397540.46113</v>
+        <v>4357413.44329</v>
       </c>
     </row>
   </sheetData>
